--- a/02_加值成品/八下/八下4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-2 影響反應速率的因素　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下4-2 影響反應速率的因素　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>濃度越大反應速率？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>越快</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>增大接觸面積</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>碰撞多</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>溫度越高反應速率？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>增大接觸面積</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>越快</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>動能大</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>顆粒越細反應速率？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>越快</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>面積大</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>能加快反應且本身不變的是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>加快</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>催化劑</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>觸媒</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>冷藏食物利用降低？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>增大接觸面積</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>更頻繁</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>減緩反應防腐</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>溫度→速率</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>保鮮</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>粉末比塊狀反應？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>快</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>接觸面積大</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>稀釋溶液反應速率會？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>變慢</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>濃度低</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>催化劑反應後質量？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>加快</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>不消耗</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>增加濃度反應速率會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>加快</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>增大接觸面積</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>濃度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>降低溫度反應速率會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>變慢</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>粉末</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>減緩反應防腐</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-2 影響反應速率的因素　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下4-2 影響反應速率的因素　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>影響反應速率四因素？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>粉末初速率快先反應完</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>濃度高單位體積粒子多碰撞頻繁</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>只變溫度,濃度面積等固定</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>濃度溫度面積催化劑</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>四項</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>提高溫度為何加快反應？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>濃度溫度面積催化劑</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>只加速達成不改變反應本質</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>只變溫度,濃度面積等固定</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>粒子動能大有效碰撞多</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>碰撞學說</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>食物冷凍比冷藏更能？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>加快</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>減緩反應防腐</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>低溫</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>催化劑如何加快反應？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>增大接觸面積</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>降低活化能</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>相同質量鐵,粉末或塊狀先反應完？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>降低活化能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>粉末</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>面積大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>雙氧水加二氧化錳分解變快,MnO₂是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>催化劑</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>更頻繁</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>觸媒</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>增加反應物濃度使碰撞？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>更頻繁</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>速率增</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>嚼碎食物幫助消化因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>更頻繁</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>增大接觸面積</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>減緩反應防腐</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>面積</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>把塊狀改成粉末反應速率？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>加快</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>面積</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>催化劑在反應前後質量？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>溫度→速率</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>不消耗</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下4-2 影響反應速率的因素　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下4-2 影響反應速率的因素　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>設計實驗驗證溫度對反應速率影響要控制什麼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>濃度溫度面積催化劑</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>更低溫更減緩反應</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>只變溫度,濃度面積等固定</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>只加速達成不改變反應本質</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>控制變因</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>催化劑為何不改變生成物總量？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>粉末初速率快先反應完</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>更低溫更減緩反應</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>只加速達成不改變反應本質</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>粒子動能大有效碰撞多</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>麵粉工廠為何有粉塵爆炸風險？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>只加速達成不改變反應本質</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>極細粉末面積大反應極快</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>濃度溫度面積催化劑</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>更低溫更減緩反應</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>面積</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>用碰撞學說解釋濃度效應？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>濃度高單位體積粒子多碰撞頻繁</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>只加速達成不改變反應本質</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>催化劑(生物催化)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>更低溫更減緩反應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>解釋</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>觸媒轉化器如何減廢氣？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>只變溫度,濃度面積等固定</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>濃度溫度面積催化劑</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>粒子動能大有效碰撞多</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>催化有害氣體轉無害</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>冰箱保鮮與哪個因素有關？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>減緩反應防腐</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>催化劑</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>低溫減緩</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>比較塊狀與粉末大理石與酸反應曲線？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>粉末初速率快先反應完</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>只加速達成不改變反應本質</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>催化有害氣體轉無害</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>只變溫度,濃度面積等固定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>圖形</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>酵素是生物體的什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>只變溫度,濃度面積等固定</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>催化劑(生物催化)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>催化有害氣體轉無害</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>濃度高單位體積粒子多碰撞頻繁</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>酶</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何食物冷凍比冷藏更耐放？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>極細粉末面積大反應極快</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>只變溫度,濃度面積等固定</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>粒子動能大有效碰撞多</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>更低溫更減緩反應</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>催化劑加快反應是藉由降低？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>活化能</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>降低活化能</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>增大接觸面積</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>碰撞多</t>
+          <t>碰撞多：濃度越高代表單位空間裡的粒子越多，粒子彼此碰撞的機會也跟著變多，反應變快</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>動能大</t>
+          <t>動能大：溫度升高會讓粒子移動得更快、帶有更多能量，能成功引發反應的碰撞也隨之增加</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>面積大</t>
+          <t>面積大：顆粒切得越細，能和其他物質接觸的表面積就越大，反應機會也就越多</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>觸媒</t>
+          <t>觸媒：催化劑能幫助反應加快進行，但它自己在反應前後的質量和性質都不會改變</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>保鮮</t>
+          <t>保鮮：低溫會讓造成食物變質的反應速率變慢，所以食物能保存得比較久</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>接觸面積大</t>
+          <t>接觸面積大：把物質磨成粉末後，能接觸到反應物的表面積大幅增加，所以反應得比塊狀快</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>濃度低</t>
+          <t>濃度低：加水稀釋後單位體積裡的粒子數量變少，碰撞機會減少，反應速率也隨之變慢</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>不消耗</t>
+          <t>不消耗：催化劑只是幫助反應更容易進行，本身並沒有真的參與反應被消耗掉，質量維持不變</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>濃度</t>
+          <t>濃度：增加反應物濃度，單位體積內粒子數變多，碰撞機會增加，反應速率會加快</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>溫度：降低溫度會使粒子運動變慢、碰撞的能量和頻率都減少，反應速率因此變慢</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>四項</t>
+          <t>四項：這四個因素分別從粒子密集程度、粒子動能、接觸機會、反應門檻高低來影響反應快慢</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>碰撞學說</t>
+          <t>碰撞學說：溫度越高粒子動得越快、能量越大，撞擊時更容易成功越過活化能，有效碰撞就變多</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>低溫</t>
+          <t>低溫：冷凍的溫度比冷藏更低，粒子動能更小，造成食物腐壞的反應速率被壓得更慢，更能防止腐敗</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：催化劑能讓反應所需跨過的能量門檻變低，粒子更容易達到條件成功反應，速率就變快</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>面積大</t>
+          <t>面積大：粉末狀的鐵接觸空氣或酸的表面積比整塊鐵大很多，所以會比塊狀更快反應完</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>觸媒</t>
+          <t>觸媒：二氧化錳幫助雙氧水更快分解出氧氣，但自己在反應前後的量都沒有改變，是典型的催化劑</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>速率增</t>
+          <t>速率增：濃度提高等於單位空間內粒子數目變多，彼此相撞的機會自然變得更頻繁</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>面積：把食物嚼碎後和消化酵素接觸的表面積變大，消化反應能進行得更快更完全</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>面積：把塊狀固體磨成粉末，能大幅增加與其他反應物接觸的表面積，有效碰撞機會增加，反應速率因此加快</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>不消耗</t>
+          <t>不消耗：催化劑只是幫助降低反應所需的活化能、加快反應速率，本身在反應前後不會被消耗，質量維持不變</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>控制變因</t>
+          <t>控制變因：為了確定是溫度造成的差異，實驗中除了溫度以外的其他條件都要保持相同，才能公平比較</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：催化劑只是幫忙讓反應更快到達終點，並不會改變反應物和生成物之間原本的量的關係</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>面積：麵粉磨得極細後和空氣接觸的表面積暴增，一遇火花就能瞬間劇烈反應，容易引發爆炸</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>解釋</t>
+          <t>解釋：溶液濃度越高，代表相同體積裡擠著越多的粒子，粒子彼此碰撞的次數自然就會變多</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：汽車排氣管裡的觸媒能幫助有害的廢氣加速反應，轉變成比較無害的氣體再排出</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>低溫減緩</t>
+          <t>低溫減緩：冰箱靠降低溫度來減緩造成食物腐壞的化學反應速率，讓食物能保存得更久</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>圖形</t>
+          <t>圖形：粉末的接觸面積大，一開始反應速率就特別快，會比同樣質量的塊狀大理石更早反應完畢</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>酶</t>
+          <t>酶：酵素是生物體內天然的催化劑，能幫助體內的化學反應更快進行，本身不被消耗</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>溫度：冷凍的溫度比冷藏更低，能讓食物內部造成腐敗的化學反應與微生物活動速率變得更慢，因此冷凍食物比冷藏更能延長保存期限</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：催化劑能提供另一條活化能較低的反應途徑，讓反應物更容易跨越能量門檻，因此加快反應速率</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下4-2_三種難度測驗卷.xlsx
@@ -573,12 +573,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>催化劑</t>
+          <t>溫度→速率</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>增大接觸面積</t>
+          <t>減緩反應防腐</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>增大接觸面積</t>
+          <t>溫度→速率</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>變慢</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>不變</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>催化劑</t>
+          <t>變慢</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>溫度</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>粉末</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>增大接觸面積</t>
+          <t>催化劑</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>更頻繁</t>
+          <t>變慢</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>減緩反應防腐</t>
+          <t>加快</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>減緩反應防腐</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>催化劑</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>溫度→速率</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>粉末</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>溫度→速率</t>
+          <t>更頻繁</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>變慢</t>
+          <t>增大接觸面積</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>增大接觸面積</t>
+          <t>溫度</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>變慢</t>
+          <t>更頻繁</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>增大接觸面積</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>溫度→速率</t>
+          <t>催化劑</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>越快</t>
+          <t>粉末</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>活化能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>溫度→速率</t>
+          <t>減緩反應防腐</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>催化劑</t>
+          <t>越快</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>降低活化能</t>
+          <t>溫度→速率</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>越快</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
